--- a/AtchisonRegime/Outputs/USA/USA_Quality/df_regTrendSummaryUSA_Quality.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA_Quality/df_regTrendSummaryUSA_Quality.xlsx
@@ -780,13 +780,13 @@
         <v>45138</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4118273717747234</v>
+        <v>0.2470415838981017</v>
       </c>
     </row>
   </sheetData>
